--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -431,202 +431,202 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_acc_fisher</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_prec_fisher</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>adj_p_rec_fisher</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tp</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tn</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fp</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fn</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_accuracy</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_accuracy</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_precision</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_precision</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_p_recall</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>fisher_adj_p_recall</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>fisher_p_f1</t>
+          <t>p_f1_fisher</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>fisher_adj_p_f1</t>
+          <t>adj_p_f1_fisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>2400</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GPT-4o base</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>788</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F2" t="n">
+        <v>116</v>
+      </c>
+      <c r="G2" t="n">
+        <v>256</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.845</v>
       </c>
-      <c r="C2" t="n">
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
         <v>0.8716814159292036</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.7547892720306514</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.809034907597536</v>
-      </c>
-      <c r="F2" t="n">
-        <v>788</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1240</v>
-      </c>
-      <c r="H2" t="n">
-        <v>116</v>
-      </c>
-      <c r="I2" t="n">
-        <v>256</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GPT-4o base</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>0.7547892720306514</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0.809034907597536</v>
+      </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2400</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GPT-4o FT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>906</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F3" t="n">
+        <v>76</v>
+      </c>
+      <c r="G3" t="n">
+        <v>138</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.9108333333333334</v>
       </c>
-      <c r="C3" t="n">
+      <c r="I3" t="n">
+        <v>3.438252644104878e-12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.402205103968926e-11</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.9226069246435845</v>
       </c>
-      <c r="D3" t="n">
+      <c r="L3" t="n">
+        <v>0.0003219270713458823</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0003863124856150587</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.867816091954023</v>
       </c>
-      <c r="E3" t="n">
+      <c r="O3" t="n">
+        <v>4.582039530868418e-11</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.374611859260525e-10</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.8943731490621916</v>
-      </c>
-      <c r="F3" t="n">
-        <v>906</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1280</v>
-      </c>
-      <c r="H3" t="n">
-        <v>76</v>
-      </c>
-      <c r="I3" t="n">
-        <v>138</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GPT-4o FT</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.438252644104878e-12</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.402205103968926e-11</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0003219270713458823</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.0003863124856150587</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.582039530868418e-11</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.374611859260525e-10</v>
       </c>
       <c r="R3" t="n">
         <v>2.880293841626032e-14</v>
@@ -636,60 +636,60 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2400</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GPT-4o QSP</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>847</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F4" t="n">
+        <v>165</v>
+      </c>
+      <c r="G4" t="n">
+        <v>197</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.8491666666666666</v>
       </c>
-      <c r="C4" t="n">
+      <c r="I4" t="n">
+        <v>0.7181658245235966</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8056061671643664</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.8369565217391305</v>
       </c>
-      <c r="D4" t="n">
+      <c r="L4" t="n">
+        <v>0.03291318749983736</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03291318749983736</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.8113026819923371</v>
       </c>
-      <c r="E4" t="n">
+      <c r="O4" t="n">
+        <v>0.00205226843449151</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.002462722121389812</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.8239299610894942</v>
-      </c>
-      <c r="F4" t="n">
-        <v>847</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1191</v>
-      </c>
-      <c r="H4" t="n">
-        <v>165</v>
-      </c>
-      <c r="I4" t="n">
-        <v>197</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GPT-4o QSP</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.7181658245235966</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8056061671643664</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.03291318749983736</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.03291318749983736</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.00205226843449151</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.002462722121389812</v>
       </c>
       <c r="R4" t="n">
         <v>0.2360575619650513</v>
@@ -699,107 +699,107 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2400</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B base</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>793</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F5" t="n">
+        <v>221</v>
+      </c>
+      <c r="G5" t="n">
+        <v>251</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.8033333333333333</v>
       </c>
-      <c r="C5" t="n">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
         <v>0.782051282051282</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.7595785440613027</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.770651117589893</v>
-      </c>
-      <c r="F5" t="n">
-        <v>793</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1135</v>
-      </c>
-      <c r="H5" t="n">
-        <v>221</v>
-      </c>
-      <c r="I5" t="n">
-        <v>251</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B base</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0.7595785440613027</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0.770651117589893</v>
+      </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>2400</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>744</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1306</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.8541666666666666</v>
       </c>
-      <c r="C6" t="n">
+      <c r="I6" t="n">
+        <v>3.439441037796223e-06</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.878882075592446e-06</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.9370277078085643</v>
       </c>
-      <c r="D6" t="n">
+      <c r="L6" t="n">
+        <v>2.259035500816541e-21</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.355421300489925e-20</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.7126436781609196</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.8095756256800871</v>
-      </c>
-      <c r="F6" t="n">
-        <v>744</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1306</v>
-      </c>
-      <c r="H6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" t="n">
-        <v>300</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B FT</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>3.439441037796223e-06</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.878882075592446e-06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.259035500816541e-21</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.355421300489925e-20</v>
+        <v>0.01710975217912993</v>
       </c>
       <c r="P6" t="n">
         <v>0.01710975217912993</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01710975217912993</v>
+        <v>0.8095756256800871</v>
       </c>
       <c r="R6" t="n">
         <v>0.003168722562459006</v>
@@ -809,60 +809,60 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2400</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B QSP</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>865</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1239</v>
+      </c>
+      <c r="F7" t="n">
+        <v>117</v>
+      </c>
+      <c r="G7" t="n">
+        <v>179</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.8766666666666667</v>
       </c>
-      <c r="C7" t="n">
+      <c r="I7" t="n">
+        <v>4.674017013229755e-12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.402205103968926e-11</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.8808553971486762</v>
       </c>
-      <c r="D7" t="n">
+      <c r="L7" t="n">
+        <v>4.033705654820302e-09</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.210111696446091e-08</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.828544061302682</v>
       </c>
-      <c r="E7" t="n">
+      <c r="O7" t="n">
+        <v>0.0001186052645544575</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.0002372105291089151</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.8538993089832182</v>
-      </c>
-      <c r="F7" t="n">
-        <v>865</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1239</v>
-      </c>
-      <c r="H7" t="n">
-        <v>117</v>
-      </c>
-      <c r="I7" t="n">
-        <v>179</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Llama3.1-70B QSP</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4.674017013229755e-12</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.402205103968926e-11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>4.033705654820302e-09</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.210111696446091e-08</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.0001186052645544575</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.0002372105291089151</v>
       </c>
       <c r="R7" t="n">
         <v>8.744174553986341e-12</v>
@@ -872,107 +872,107 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>2400</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B base</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>700</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1181</v>
+      </c>
+      <c r="F8" t="n">
+        <v>175</v>
+      </c>
+      <c r="G8" t="n">
+        <v>344</v>
+      </c>
+      <c r="H8" t="n">
         <v>0.7837499999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
         <v>0.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6704980842911877</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.7295466388744136</v>
-      </c>
-      <c r="F8" t="n">
-        <v>700</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1181</v>
-      </c>
-      <c r="H8" t="n">
-        <v>175</v>
-      </c>
-      <c r="I8" t="n">
-        <v>344</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B base</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>0.6704980842911877</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>0.7295466388744136</v>
+      </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>2400</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>624</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F9" t="n">
+        <v>82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>420</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.7908333333333334</v>
       </c>
-      <c r="C9" t="n">
+      <c r="I9" t="n">
+        <v>0.5725376741703739</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8056061671643664</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.8838526912181303</v>
       </c>
-      <c r="D9" t="n">
+      <c r="L9" t="n">
+        <v>7.596222518105277e-06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.321343303672412e-05</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.5977011494252874</v>
       </c>
-      <c r="E9" t="n">
+      <c r="O9" t="n">
+        <v>0.0006510696776927115</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0009766045165390672</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.7131428571428572</v>
-      </c>
-      <c r="F9" t="n">
-        <v>624</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1274</v>
-      </c>
-      <c r="H9" t="n">
-        <v>82</v>
-      </c>
-      <c r="I9" t="n">
-        <v>420</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B FT</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5725376741703739</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.8056061671643664</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7.596222518105277e-06</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.321343303672412e-05</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.0006510696776927115</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.0009766045165390672</v>
       </c>
       <c r="R9" t="n">
         <v>0.2688783553575099</v>
@@ -982,60 +982,60 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Partial Match</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>2400</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B QSP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>885</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F10" t="n">
+        <v>352</v>
+      </c>
+      <c r="G10" t="n">
+        <v>159</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.7870833333333334</v>
       </c>
-      <c r="C10" t="n">
+      <c r="I10" t="n">
+        <v>0.8056061671643664</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8056061671643664</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.7154405820533549</v>
       </c>
-      <c r="D10" t="n">
+      <c r="L10" t="n">
+        <v>8.808955357816084e-06</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.321343303672412e-05</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.8477011494252874</v>
       </c>
-      <c r="E10" t="n">
+      <c r="O10" t="n">
+        <v>2.061025596110011e-21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.236615357666007e-20</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.7759754493643138</v>
-      </c>
-      <c r="F10" t="n">
-        <v>885</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1004</v>
-      </c>
-      <c r="H10" t="n">
-        <v>352</v>
-      </c>
-      <c r="I10" t="n">
-        <v>159</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Llama3.1-8B QSP</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.8056061671643664</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.8056061671643664</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8.808955357816084e-06</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.321343303672412e-05</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.061025596110011e-21</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.236615357666007e-20</v>
       </c>
       <c r="R10" t="n">
         <v>0.0005452100820346853</v>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>788</v>
+        <v>756</v>
       </c>
       <c r="E2" t="n">
         <v>1240</v>
@@ -549,25 +549,25 @@
         <v>116</v>
       </c>
       <c r="G2" t="n">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="H2" t="n">
-        <v>0.845</v>
+        <v>0.8316666666666667</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.8716814159292036</v>
+        <v>0.8669724770642202</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.7547892720306514</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.809034907597536</v>
+        <v>0.7891440501043843</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>906</v>
+        <v>880</v>
       </c>
       <c r="E3" t="n">
         <v>1280</v>
@@ -596,43 +596,43 @@
         <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9108333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>3.438252644104878e-12</v>
+        <v>4.063801112646733e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>1.402205103968926e-11</v>
+        <v>2.43828066758804e-11</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9226069246435845</v>
+        <v>0.9205020920502092</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003219270713458823</v>
+        <v>0.0002324380349709392</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003863124856150587</v>
+        <v>0.0002789256419651271</v>
       </c>
       <c r="N3" t="n">
-        <v>0.867816091954023</v>
+        <v>0.842911877394636</v>
       </c>
       <c r="O3" t="n">
-        <v>4.582039530868418e-11</v>
+        <v>5.087639395447718e-11</v>
       </c>
       <c r="P3" t="n">
-        <v>1.374611859260525e-10</v>
+        <v>1.526291818634316e-10</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8943731490621916</v>
+        <v>0.88</v>
       </c>
       <c r="R3" t="n">
-        <v>2.880293841626032e-14</v>
+        <v>1.699770095447303e-14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.72817630497562e-13</v>
+        <v>1.019862057268382e-13</v>
       </c>
     </row>
     <row r="4">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>847</v>
+        <v>817</v>
       </c>
       <c r="E4" t="n">
         <v>1191</v>
@@ -659,43 +659,43 @@
         <v>165</v>
       </c>
       <c r="G4" t="n">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8491666666666666</v>
+        <v>0.8366666666666667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7181658245235966</v>
+        <v>0.6694826441336608</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8056061671643664</v>
+        <v>0.803379172960393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8369565217391305</v>
+        <v>0.8319755600814664</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03291318749983736</v>
+        <v>0.03791782290596404</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03291318749983736</v>
+        <v>0.03791782290596404</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8113026819923371</v>
+        <v>0.7825670498084292</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00205226843449151</v>
+        <v>0.002299573251550029</v>
       </c>
       <c r="P4" t="n">
-        <v>0.002462722121389812</v>
+        <v>0.002759487901860035</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8239299610894942</v>
+        <v>0.8065153010858837</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2360575619650513</v>
+        <v>0.1773629944776504</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2688783553575099</v>
+        <v>0.2128355933731805</v>
       </c>
     </row>
     <row r="5">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>793</v>
+        <v>769</v>
       </c>
       <c r="E5" t="n">
         <v>1135</v>
@@ -722,25 +722,25 @@
         <v>221</v>
       </c>
       <c r="G5" t="n">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8033333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0.782051282051282</v>
+        <v>0.7767676767676768</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.7595785440613027</v>
+        <v>0.7365900383141762</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>0.770651117589893</v>
+        <v>0.7561455260570304</v>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="E6" t="n">
         <v>1306</v>
@@ -769,43 +769,43 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8504166666666667</v>
       </c>
       <c r="I6" t="n">
-        <v>3.439441037796223e-06</v>
+        <v>2.759979691002629e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>6.878882075592446e-06</v>
+        <v>5.519959382005258e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9370277078085643</v>
+        <v>0.9363057324840764</v>
       </c>
       <c r="L6" t="n">
-        <v>2.259035500816541e-21</v>
+        <v>5.865795631479074e-22</v>
       </c>
       <c r="M6" t="n">
-        <v>1.355421300489925e-20</v>
+        <v>3.519477378887445e-21</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7126436781609196</v>
+        <v>0.7040229885057471</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01710975217912993</v>
+        <v>0.1075784234263296</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01710975217912993</v>
+        <v>0.1075784234263296</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8095756256800871</v>
+        <v>0.8037178786221978</v>
       </c>
       <c r="R6" t="n">
-        <v>0.003168722562459006</v>
+        <v>0.0004092429143765511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00475308384368851</v>
+        <v>0.0008184858287531021</v>
       </c>
     </row>
     <row r="7">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>865</v>
+        <v>832</v>
       </c>
       <c r="E7" t="n">
         <v>1239</v>
@@ -832,43 +832,43 @@
         <v>117</v>
       </c>
       <c r="G7" t="n">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8766666666666667</v>
+        <v>0.8629166666666667</v>
       </c>
       <c r="I7" t="n">
-        <v>4.674017013229755e-12</v>
+        <v>1.907735331657031e-10</v>
       </c>
       <c r="J7" t="n">
-        <v>1.402205103968926e-11</v>
+        <v>5.723205994971095e-10</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8808553971486762</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="L7" t="n">
-        <v>4.033705654820302e-09</v>
+        <v>7.468142128511194e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.210111696446091e-08</v>
+        <v>2.240442638553358e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>0.828544061302682</v>
+        <v>0.7969348659003831</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001186052645544575</v>
+        <v>0.00132015147909362</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0002372105291089151</v>
+        <v>0.00198022721864043</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8538993089832182</v>
+        <v>0.8349222277972904</v>
       </c>
       <c r="R7" t="n">
-        <v>8.744174553986341e-12</v>
+        <v>6.25788121234414e-10</v>
       </c>
       <c r="S7" t="n">
-        <v>2.623252366195903e-11</v>
+        <v>1.877364363703242e-09</v>
       </c>
     </row>
     <row r="8">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="E8" t="n">
         <v>1181</v>
@@ -895,25 +895,25 @@
         <v>175</v>
       </c>
       <c r="G8" t="n">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7837499999999999</v>
+        <v>0.7758333333333334</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.8</v>
+        <v>0.7955607476635514</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.6704980842911877</v>
+        <v>0.6522988505747126</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>0.7295466388744136</v>
+        <v>0.7168421052631578</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="E9" t="n">
         <v>1274</v>
@@ -942,43 +942,43 @@
         <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7908333333333334</v>
+        <v>0.7837499999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5725376741703739</v>
+        <v>0.5306921551564537</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8056061671643664</v>
+        <v>0.7960382327346807</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8838526912181303</v>
+        <v>0.8809869375907112</v>
       </c>
       <c r="L9" t="n">
-        <v>7.596222518105277e-06</v>
+        <v>7.272402933308455e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>1.321343303672412e-05</v>
+        <v>1.090860439996268e-05</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5977011494252874</v>
+        <v>0.5814176245210728</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0006510696776927115</v>
+        <v>0.001010025069857984</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0009766045165390672</v>
+        <v>0.00198022721864043</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7131428571428572</v>
+        <v>0.7005193306405079</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2688783553575099</v>
+        <v>0.2890007464688449</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2688783553575099</v>
+        <v>0.2890007464688449</v>
       </c>
     </row>
     <row r="10">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="E10" t="n">
         <v>1004</v>
@@ -1005,43 +1005,43 @@
         <v>352</v>
       </c>
       <c r="G10" t="n">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7870833333333334</v>
+        <v>0.7729166666666667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8056061671643664</v>
+        <v>0.8358715815339177</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8056061671643664</v>
+        <v>0.8358715815339176</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7154405820533549</v>
+        <v>0.7073981712385703</v>
       </c>
       <c r="L10" t="n">
-        <v>8.808955357816084e-06</v>
+        <v>6.28988912973865e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>1.321343303672412e-05</v>
+        <v>1.090860439996268e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8477011494252874</v>
+        <v>0.8151340996168582</v>
       </c>
       <c r="O10" t="n">
-        <v>2.061025596110011e-21</v>
+        <v>3.836597907936616e-17</v>
       </c>
       <c r="P10" t="n">
-        <v>1.236615357666007e-20</v>
+        <v>2.30195874476197e-16</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7759754493643138</v>
+        <v>0.757454383622608</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0005452100820346853</v>
+        <v>0.003228200629532775</v>
       </c>
       <c r="S10" t="n">
-        <v>0.001090420164069371</v>
+        <v>0.004842300944299163</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -425,623 +425,747 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>scenario</t>
+          <t>samples</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>samples</t>
+          <t>model</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>tp</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tp</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tn</t>
+          <t>fp</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>fp</t>
+          <t>fn</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>fn</t>
+          <t>accuracy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>p_acc_fisher</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>p_acc_fisher</t>
+          <t>adj_p_acc_fisher</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_acc_fisher</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>p_prec_fisher</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>p_prec_fisher</t>
+          <t>adj_p_prec_fisher</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_prec_fisher</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>p_rec_fisher</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>p_rec_fisher</t>
+          <t>adj_p_rec_fisher</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>adj_p_rec_fisher</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>p_f1_fisher</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>p_f1_fisher</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
           <t>adj_p_f1_fisher</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>2400</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>GPT-4o base</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>765</v>
+      </c>
       <c r="D2" t="n">
-        <v>756</v>
+        <v>1240</v>
       </c>
       <c r="E2" t="n">
-        <v>1240</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>116</v>
+        <v>279</v>
       </c>
       <c r="G2" t="n">
-        <v>288</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8316666666666667</v>
-      </c>
+        <v>0.8354166666666667</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0.8669724770642202</v>
-      </c>
+      <c r="J2" t="n">
+        <v>0.8683314415437003</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0.7241379310344828</v>
-      </c>
+      <c r="M2" t="n">
+        <v>0.7327586206896551</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>0.7891440501043843</v>
-      </c>
+      <c r="P2" t="n">
+        <v>0.7948051948051947</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>2400</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>GPT-4o FT</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>882</v>
+      </c>
       <c r="D3" t="n">
-        <v>880</v>
+        <v>1280</v>
       </c>
       <c r="E3" t="n">
-        <v>1280</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="G3" t="n">
-        <v>164</v>
+        <v>0.9008333333333334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>2.323766362037916e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>4.063801112646733e-12</v>
+        <v>5.228474314585311e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>2.43828066758804e-11</v>
+        <v>0.9206680584551148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9205020920502092</v>
+        <v>0.000315172981821217</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002324380349709392</v>
+        <v>0.0004052224051987076</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002789256419651271</v>
+        <v>0.8448275862068966</v>
       </c>
       <c r="N3" t="n">
-        <v>0.842911877394636</v>
+        <v>4.148523641433452e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>5.087639395447718e-11</v>
+        <v>1.244557092430036e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>1.526291818634316e-10</v>
+        <v>0.8811188811188811</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.88</v>
+        <v>1.73189716256553e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>1.699770095447303e-14</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.019862057268382e-13</v>
+        <v>7.793537231544884e-13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>2400</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GPT-4o FT+QSP</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>867</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1241</v>
+      </c>
+      <c r="E4" t="n">
+        <v>115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>177</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8783333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.550023196890925e-05</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.825034795336388e-05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8828920570264766</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3603380114804925</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3603380114804925</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8304597701149425</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.003787616455662e-08</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.800852213702524e-07</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8558736426456071</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.471106774174149e-07</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.047992193513469e-07</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>GPT-4o QSP</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>817</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="C5" t="n">
+        <v>833</v>
+      </c>
+      <c r="D5" t="n">
         <v>1191</v>
       </c>
-      <c r="F4" t="n">
+      <c r="E5" t="n">
         <v>165</v>
       </c>
-      <c r="G4" t="n">
-        <v>227</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8366666666666667</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.6694826441336608</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.803379172960393</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8319755600814664</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.03791782290596404</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.03791782290596404</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.7825670498084292</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.002299573251550029</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.002759487901860035</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8065153010858837</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1773629944776504</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2128355933731805</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="F5" t="n">
+        <v>211</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8433333333333334</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4792313760904459</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6161546264020019</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8346693386773547</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04447699627698107</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0500366208116037</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7978927203065134</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0005327288030832841</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005993199034686947</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8158667972575906</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09978483484633351</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1122579392021252</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>2400</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Llama3.1-70B base</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>769</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C6" t="n">
+        <v>778</v>
+      </c>
+      <c r="D6" t="n">
         <v>1135</v>
       </c>
-      <c r="F5" t="n">
+      <c r="E6" t="n">
         <v>221</v>
       </c>
-      <c r="G5" t="n">
-        <v>275</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.7933333333333333</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0.7767676767676768</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>0.7365900383141762</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>0.7561455260570304</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="F6" t="n">
+        <v>266</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7970833333333334</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.7787787787787788</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0.7452107279693486</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0.7616250611845327</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>2400</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Llama3.1-70B FT</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>735</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="C7" t="n">
+        <v>737</v>
+      </c>
+      <c r="D7" t="n">
         <v>1306</v>
       </c>
-      <c r="F6" t="n">
+      <c r="E7" t="n">
         <v>50</v>
       </c>
-      <c r="G6" t="n">
-        <v>309</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8504166666666667</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.759979691002629e-07</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.519959382005258e-07</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9363057324840764</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5.865795631479074e-22</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.519477378887445e-21</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.7040229885057471</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.1075784234263296</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1075784234263296</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.8037178786221978</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.0004092429143765511</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.0008184858287531021</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="F7" t="n">
+        <v>307</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.85125</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.642008357926922e-07</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.735561504426846e-06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9364675984752223</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.12535906469232e-21</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.064115791115439e-21</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7059386973180076</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04974014237731975</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04974014237731975</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8050245767340252</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.001207111660703301</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.00155200070661853</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>2400</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Llama3.1-70B FT+QSP</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>850</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1239</v>
+      </c>
+      <c r="E8" t="n">
+        <v>117</v>
+      </c>
+      <c r="F8" t="n">
+        <v>194</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8704166666666666</v>
+      </c>
+      <c r="H8" t="n">
+        <v>9.947065105306041e-12</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.984119531591813e-11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8790072388831437</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.831729976323264e-09</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.621392446727344e-09</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.814176245210728</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001736350027133316</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0002604525040699974</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8453505718547986</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.147118476844556e-11</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.83101657290025e-11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Llama3.1-70B QSP</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>832</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="C9" t="n">
+        <v>850</v>
+      </c>
+      <c r="D9" t="n">
         <v>1239</v>
       </c>
-      <c r="F7" t="n">
+      <c r="E9" t="n">
         <v>117</v>
       </c>
-      <c r="G7" t="n">
-        <v>212</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8629166666666667</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.907735331657031e-10</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.723205994971095e-10</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8767123287671232</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7.468142128511194e-09</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2.240442638553358e-08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.7969348659003831</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.00132015147909362</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.00198022721864043</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8349222277972904</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6.25788121234414e-10</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.877364363703242e-09</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+      <c r="F9" t="n">
+        <v>194</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8704166666666666</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.947065105306041e-12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.984119531591813e-11</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8790072388831437</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.831729976323264e-09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.621392446727344e-09</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.814176245210728</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001736350027133316</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002604525040699974</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.8453505718547986</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.147118476844556e-11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.83101657290025e-11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>2400</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Llama3.1-8B base</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>681</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C10" t="n">
+        <v>689</v>
+      </c>
+      <c r="D10" t="n">
         <v>1181</v>
       </c>
-      <c r="F8" t="n">
+      <c r="E10" t="n">
         <v>175</v>
       </c>
-      <c r="G8" t="n">
-        <v>363</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.7758333333333334</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0.7955607476635514</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>0.6522988505747126</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>0.7168421052631578</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+      <c r="F10" t="n">
+        <v>355</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7791666666666667</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.7974537037037037</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>0.6599616858237548</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>0.7222222222222223</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>2400</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Llama3.1-8B FT</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>607</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="C11" t="n">
+        <v>611</v>
+      </c>
+      <c r="D11" t="n">
         <v>1274</v>
       </c>
-      <c r="F9" t="n">
+      <c r="E11" t="n">
         <v>82</v>
       </c>
-      <c r="G9" t="n">
-        <v>437</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7837499999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.5306921551564537</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7960382327346807</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8809869375907112</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.272402933308455e-06</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.090860439996268e-05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.5814176245210728</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.001010025069857984</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.00198022721864043</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.7005193306405079</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.2890007464688449</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.2890007464688449</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Partial Match</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+      <c r="F11" t="n">
+        <v>433</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7854166666666667</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.624394933262757</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7024442999206015</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8816738816738817</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7.550965306359905e-06</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.27222040446872e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.5852490421455939</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005046640889555589</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005993199034686947</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7035118019573979</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2127837724169632</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2127837724169632</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>2400</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Llama3.1-8B FT+QSP</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>323</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E12" t="n">
+        <v>344</v>
+      </c>
+      <c r="F12" t="n">
+        <v>721</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.94684130531203e-61</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.452157174780827e-60</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4842578710644678</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.570016909406745e-38</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.813015218466071e-37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3093869731800766</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.068450032438953e-58</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9.616050291950575e-58</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3775569842197545</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.186998000230892e-98</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.768298200207803e-97</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Llama3.1-8B QSP</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>851</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="C13" t="n">
+        <v>870</v>
+      </c>
+      <c r="D13" t="n">
         <v>1004</v>
       </c>
-      <c r="F10" t="n">
+      <c r="E13" t="n">
         <v>352</v>
       </c>
-      <c r="G10" t="n">
-        <v>193</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7729166666666667</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.8358715815339177</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.8358715815339176</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.7073981712385703</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.28988912973865e-06</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.090860439996268e-05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8151340996168582</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.836597907936616e-17</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.30195874476197e-16</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.757454383622608</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.003228200629532775</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.004842300944299163</v>
+      <c r="F13" t="n">
+        <v>174</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7808333333333334</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9167525979462349</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9167525979462349</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.7119476268412439</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.481469363124802e-06</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.27222040446872e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N13" t="n">
+        <v>7.045503772627296e-20</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.170476697682283e-19</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.767872903795234</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0007789024323932834</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.001168353648589925</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D2" t="n">
         <v>1240</v>
@@ -539,25 +539,25 @@
         <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8354166666666667</v>
+        <v>0.835</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8683314415437003</v>
+        <v>0.8681818181818182</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7327586206896551</v>
+        <v>0.7318007662835249</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7948051948051947</v>
+        <v>0.7941787941787941</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -587,37 +587,37 @@
         <v>0.9008333333333334</v>
       </c>
       <c r="H3" t="n">
-        <v>2.323766362037916e-11</v>
+        <v>1.783615866938336e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>5.228474314585311e-11</v>
+        <v>4.013135700611255e-11</v>
       </c>
       <c r="J3" t="n">
         <v>0.9206680584551148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000315172981821217</v>
+        <v>0.0002426192852128931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004052224051987076</v>
+        <v>0.0003119390809880054</v>
       </c>
       <c r="M3" t="n">
         <v>0.8448275862068966</v>
       </c>
       <c r="N3" t="n">
-        <v>4.148523641433452e-10</v>
+        <v>3.02765131940777e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.244557092430036e-09</v>
+        <v>9.08295395822331e-10</v>
       </c>
       <c r="P3" t="n">
         <v>0.8811188811188811</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73189716256553e-13</v>
+        <v>1.26986545870891e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>7.793537231544884e-13</v>
+        <v>5.714394564190096e-13</v>
       </c>
     </row>
     <row r="4">
@@ -645,37 +645,37 @@
         <v>0.8783333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>2.550023196890925e-05</v>
+        <v>2.14590095118893e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.825034795336388e-05</v>
+        <v>3.218851426783395e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3603380114804925</v>
+        <v>0.3601858815961053</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3603380114804925</v>
+        <v>0.3601858815961053</v>
       </c>
       <c r="M4" t="n">
         <v>0.8304597701149425</v>
       </c>
       <c r="N4" t="n">
-        <v>8.003787616455662e-08</v>
+        <v>6.088424542278483e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.800852213702524e-07</v>
+        <v>1.369895522012659e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8558736426456071</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.471106774174149e-07</v>
+        <v>3.618082810248584e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.047992193513469e-07</v>
+        <v>6.512549058447451e-07</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.8433333333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4792313760904459</v>
+        <v>0.4553901067585051</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6161546264020019</v>
+        <v>0.5855015658323637</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04447699627698107</v>
+        <v>0.04453936442729994</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0500366208116037</v>
+        <v>0.05010678498071244</v>
       </c>
       <c r="M5" t="n">
         <v>0.7978927203065134</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005327288030832841</v>
+        <v>0.0004429715057418754</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0005993199034686947</v>
+        <v>0.0005695347930966969</v>
       </c>
       <c r="P5" t="n">
         <v>0.8158667972575906</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09978483484633351</v>
+        <v>0.09191483445756859</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1122579392021252</v>
+        <v>0.1034041887647647</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D6" t="n">
         <v>1135</v>
@@ -755,25 +755,25 @@
         <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7970833333333334</v>
+        <v>0.7966666666666666</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7787787787787788</v>
+        <v>0.7785571142284569</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7452107279693486</v>
+        <v>0.7442528735632183</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7616250611845327</v>
+        <v>0.7610186092066601</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -803,37 +803,37 @@
         <v>0.85125</v>
       </c>
       <c r="H7" t="n">
-        <v>9.642008357926922e-07</v>
+        <v>8.031929076040189e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.735561504426846e-06</v>
+        <v>1.445747233687234e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9364675984752223</v>
       </c>
       <c r="K7" t="n">
-        <v>1.12535906469232e-21</v>
+        <v>1.09536713296107e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>5.064115791115439e-21</v>
+        <v>4.929152098324816e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7059386973180076</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04974014237731975</v>
+        <v>0.0558672218848466</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04974014237731975</v>
+        <v>0.05586722188484659</v>
       </c>
       <c r="P7" t="n">
         <v>0.8050245767340252</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001207111660703301</v>
+        <v>0.0009273099621365588</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00155200070661853</v>
+        <v>0.001192255665604147</v>
       </c>
     </row>
     <row r="8">
@@ -861,37 +861,37 @@
         <v>0.8704166666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>9.947065105306041e-12</v>
+        <v>7.758263820081272e-12</v>
       </c>
       <c r="I8" t="n">
-        <v>2.984119531591813e-11</v>
+        <v>2.327479146024382e-11</v>
       </c>
       <c r="J8" t="n">
         <v>0.8790072388831437</v>
       </c>
       <c r="K8" t="n">
-        <v>3.831729976323264e-09</v>
+        <v>3.800483870308596e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>8.621392446727344e-09</v>
+        <v>8.551088708194341e-09</v>
       </c>
       <c r="M8" t="n">
         <v>0.814176245210728</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001736350027133316</v>
+        <v>0.0001420109393108276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002604525040699974</v>
+        <v>0.0002130164089662414</v>
       </c>
       <c r="P8" t="n">
         <v>0.8453505718547986</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.147118476844556e-11</v>
+        <v>1.66488425149846e-11</v>
       </c>
       <c r="R8" t="n">
-        <v>4.83101657290025e-11</v>
+        <v>3.745989565871534e-11</v>
       </c>
     </row>
     <row r="9">
@@ -919,37 +919,37 @@
         <v>0.8704166666666666</v>
       </c>
       <c r="H9" t="n">
-        <v>9.947065105306041e-12</v>
+        <v>7.758263820081272e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>2.984119531591813e-11</v>
+        <v>2.327479146024382e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
       </c>
       <c r="K9" t="n">
-        <v>3.831729976323264e-09</v>
+        <v>3.800483870308596e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>8.621392446727344e-09</v>
+        <v>8.551088708194341e-09</v>
       </c>
       <c r="M9" t="n">
         <v>0.814176245210728</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001736350027133316</v>
+        <v>0.0001420109393108276</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002604525040699974</v>
+        <v>0.0002130164089662414</v>
       </c>
       <c r="P9" t="n">
         <v>0.8453505718547986</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.147118476844556e-11</v>
+        <v>1.66488425149846e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>4.83101657290025e-11</v>
+        <v>3.745989565871534e-11</v>
       </c>
     </row>
     <row r="10">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D10" t="n">
         <v>1181</v>
@@ -971,25 +971,25 @@
         <v>175</v>
       </c>
       <c r="F10" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7791666666666667</v>
+        <v>0.7787500000000001</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.7974537037037037</v>
+        <v>0.7972190034762456</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.6599616858237548</v>
+        <v>0.6590038314176245</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.7222222222222223</v>
+        <v>0.7215521761929733</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1019,37 +1019,37 @@
         <v>0.7854166666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>0.624394933262757</v>
+        <v>0.5999831421697411</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7024442999206015</v>
+        <v>0.6749810349409587</v>
       </c>
       <c r="J11" t="n">
         <v>0.8816738816738817</v>
       </c>
       <c r="K11" t="n">
-        <v>7.550965306359905e-06</v>
+        <v>7.471933906814893e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27222040446872e-05</v>
+        <v>1.344948103226681e-05</v>
       </c>
       <c r="M11" t="n">
         <v>0.5852490421455939</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005046640889555589</v>
+        <v>0.0005987452412680276</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0005993199034686947</v>
+        <v>0.0006735883964265311</v>
       </c>
       <c r="P11" t="n">
         <v>0.7035118019573979</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2127837724169632</v>
+        <v>0.2407683837052523</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2127837724169632</v>
+        <v>0.2407683837052524</v>
       </c>
     </row>
     <row r="12">
@@ -1077,37 +1077,37 @@
         <v>0.55625</v>
       </c>
       <c r="H12" t="n">
-        <v>4.94684130531203e-61</v>
+        <v>8.68670702162462e-61</v>
       </c>
       <c r="I12" t="n">
-        <v>4.452157174780827e-60</v>
+        <v>7.818036319462158e-60</v>
       </c>
       <c r="J12" t="n">
         <v>0.4842578710644678</v>
       </c>
       <c r="K12" t="n">
-        <v>7.570016909406745e-38</v>
+        <v>8.318099831966586e-38</v>
       </c>
       <c r="L12" t="n">
-        <v>6.813015218466071e-37</v>
+        <v>7.486289848769928e-37</v>
       </c>
       <c r="M12" t="n">
         <v>0.3093869731800766</v>
       </c>
       <c r="N12" t="n">
-        <v>1.068450032438953e-58</v>
+        <v>2.203485762983409e-58</v>
       </c>
       <c r="O12" t="n">
-        <v>9.616050291950575e-58</v>
+        <v>1.983137186685068e-57</v>
       </c>
       <c r="P12" t="n">
         <v>0.3775569842197545</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.186998000230892e-98</v>
+        <v>9.216498974084533e-98</v>
       </c>
       <c r="R12" t="n">
-        <v>3.768298200207803e-97</v>
+        <v>8.29484907667608e-97</v>
       </c>
     </row>
     <row r="13">
@@ -1135,37 +1135,37 @@
         <v>0.7808333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9167525979462349</v>
+        <v>0.8891975855015103</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9167525979462349</v>
+        <v>0.8891975855015103</v>
       </c>
       <c r="J13" t="n">
         <v>0.7119476268412439</v>
       </c>
       <c r="K13" t="n">
-        <v>8.481469363124802e-06</v>
+        <v>1.048038688026416e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27222040446872e-05</v>
+        <v>1.572058032039625e-05</v>
       </c>
       <c r="M13" t="n">
         <v>0.8333333333333334</v>
       </c>
       <c r="N13" t="n">
-        <v>7.045503772627296e-20</v>
+        <v>4.623550295738242e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>3.170476697682283e-19</v>
+        <v>2.080597633082209e-19</v>
       </c>
       <c r="P13" t="n">
         <v>0.767872903795234</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0007789024323932834</v>
+        <v>0.0006845637960723105</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001168353648589925</v>
+        <v>0.001026845694108466</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -590,7 +590,7 @@
         <v>1.783615866938336e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>4.013135700611255e-11</v>
+        <v>5.350847600815007e-11</v>
       </c>
       <c r="J3" t="n">
         <v>0.9206680584551148</v>
@@ -608,7 +608,7 @@
         <v>3.02765131940777e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>9.08295395822331e-10</v>
+        <v>1.362443093733496e-09</v>
       </c>
       <c r="P3" t="n">
         <v>0.8811188811188811</v>
@@ -617,7 +617,7 @@
         <v>1.26986545870891e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>5.714394564190096e-13</v>
+        <v>1.142878912838019e-12</v>
       </c>
     </row>
     <row r="4">
@@ -666,7 +666,7 @@
         <v>6.088424542278483e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.369895522012659e-07</v>
+        <v>1.826527362683545e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8558736426456071</v>
@@ -815,7 +815,7 @@
         <v>1.09536713296107e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>4.929152098324816e-21</v>
+        <v>9.858304196649632e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7059386973180076</v>
@@ -864,7 +864,7 @@
         <v>7.758263820081272e-12</v>
       </c>
       <c r="I8" t="n">
-        <v>2.327479146024382e-11</v>
+        <v>3.491218719036573e-11</v>
       </c>
       <c r="J8" t="n">
         <v>0.8790072388831437</v>
@@ -873,7 +873,7 @@
         <v>3.800483870308596e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>8.551088708194341e-09</v>
+        <v>1.140145161092579e-08</v>
       </c>
       <c r="M8" t="n">
         <v>0.814176245210728</v>
@@ -882,7 +882,7 @@
         <v>0.0001420109393108276</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002130164089662414</v>
+        <v>0.0002556196907594897</v>
       </c>
       <c r="P8" t="n">
         <v>0.8453505718547986</v>
@@ -891,7 +891,7 @@
         <v>1.66488425149846e-11</v>
       </c>
       <c r="R8" t="n">
-        <v>3.745989565871534e-11</v>
+        <v>4.994652754495379e-11</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>7.758263820081272e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>2.327479146024382e-11</v>
+        <v>3.491218719036573e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
@@ -931,7 +931,7 @@
         <v>3.800483870308596e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>8.551088708194341e-09</v>
+        <v>1.140145161092579e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.814176245210728</v>
@@ -940,7 +940,7 @@
         <v>0.0001420109393108276</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002130164089662414</v>
+        <v>0.0002556196907594897</v>
       </c>
       <c r="P9" t="n">
         <v>0.8453505718547986</v>
@@ -949,7 +949,7 @@
         <v>1.66488425149846e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>3.745989565871534e-11</v>
+        <v>4.994652754495379e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1062,52 +1062,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>323</v>
+        <v>605</v>
       </c>
       <c r="D12" t="n">
-        <v>1012</v>
+        <v>1087</v>
       </c>
       <c r="E12" t="n">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="F12" t="n">
-        <v>721</v>
+        <v>439</v>
       </c>
       <c r="G12" t="n">
-        <v>0.55625</v>
+        <v>0.705</v>
       </c>
       <c r="H12" t="n">
-        <v>8.68670702162462e-61</v>
+        <v>6.154608721883135e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>7.818036319462158e-60</v>
+        <v>1.384786962423705e-08</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4842578710644678</v>
+        <v>0.6922196796338673</v>
       </c>
       <c r="K12" t="n">
-        <v>8.318099831966586e-38</v>
+        <v>5.327992049463875e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>7.486289848769928e-37</v>
+        <v>1.198798211129372e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3093869731800766</v>
+        <v>0.5795019157088123</v>
       </c>
       <c r="N12" t="n">
-        <v>2.203485762983409e-58</v>
+        <v>0.0002172866910617807</v>
       </c>
       <c r="O12" t="n">
-        <v>1.983137186685068e-57</v>
+        <v>0.0003259300365926711</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3775569842197545</v>
+        <v>0.6308654848800835</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.216498974084533e-98</v>
+        <v>2.184513065566583e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>8.29484907667608e-97</v>
+        <v>4.915154397524811e-09</v>
       </c>
     </row>
     <row r="13">
@@ -1156,7 +1156,7 @@
         <v>4.623550295738242e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>2.080597633082209e-19</v>
+        <v>4.161195266164418e-19</v>
       </c>
       <c r="P13" t="n">
         <v>0.767872903795234</v>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -590,7 +590,7 @@
         <v>1.783615866938336e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>5.350847600815007e-11</v>
+        <v>8.02627140122251e-11</v>
       </c>
       <c r="J3" t="n">
         <v>0.9206680584551148</v>
@@ -648,7 +648,7 @@
         <v>2.14590095118893e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.218851426783395e-05</v>
+        <v>3.862621712140074e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
@@ -675,7 +675,7 @@
         <v>3.618082810248584e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>6.512549058447451e-07</v>
+        <v>8.140686323059314e-07</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v>0.09191483445756859</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1034041887647647</v>
+        <v>0.1181762157311596</v>
       </c>
     </row>
     <row r="6">
@@ -806,7 +806,7 @@
         <v>8.031929076040189e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.445747233687234e-06</v>
+        <v>1.807184042109043e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9364675984752223</v>
@@ -815,7 +815,7 @@
         <v>1.09536713296107e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>9.858304196649632e-21</v>
+        <v>4.929152098324816e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7059386973180076</v>
@@ -833,7 +833,7 @@
         <v>0.0009273099621365588</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001192255665604147</v>
+        <v>0.001390964943204838</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>850</v>
+        <v>668</v>
       </c>
       <c r="D8" t="n">
-        <v>1239</v>
+        <v>1321</v>
       </c>
       <c r="E8" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>194</v>
+        <v>376</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8704166666666666</v>
+        <v>0.82875</v>
       </c>
       <c r="H8" t="n">
-        <v>7.758263820081272e-12</v>
+        <v>0.004909853445594204</v>
       </c>
       <c r="I8" t="n">
-        <v>3.491218719036573e-11</v>
+        <v>0.007364780168391307</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8790072388831437</v>
+        <v>0.9502133712660028</v>
       </c>
       <c r="K8" t="n">
-        <v>3.800483870308596e-09</v>
+        <v>5.768561548496698e-25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.140145161092579e-08</v>
+        <v>5.191705393647028e-24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.814176245210728</v>
+        <v>0.6398467432950191</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0001420109393108276</v>
+        <v>2.919623911647553e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0002556196907594897</v>
+        <v>6.569153801206996e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8453505718547986</v>
+        <v>0.7647395535203205</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.66488425149846e-11</v>
+        <v>0.8182340598783613</v>
       </c>
       <c r="R8" t="n">
-        <v>4.994652754495379e-11</v>
+        <v>0.8182340598783613</v>
       </c>
     </row>
     <row r="9">
@@ -922,7 +922,7 @@
         <v>7.758263820081272e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>3.491218719036573e-11</v>
+        <v>6.982437438073145e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
@@ -949,7 +949,7 @@
         <v>1.66488425149846e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>4.994652754495379e-11</v>
+        <v>7.491979131743069e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1049,7 +1049,7 @@
         <v>0.2407683837052523</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2407683837052524</v>
+        <v>0.2708644316684089</v>
       </c>
     </row>
     <row r="12">
@@ -1080,7 +1080,7 @@
         <v>6.154608721883135e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>1.384786962423705e-08</v>
+        <v>1.84638261656494e-08</v>
       </c>
       <c r="J12" t="n">
         <v>0.6922196796338673</v>
@@ -1107,7 +1107,7 @@
         <v>2.184513065566583e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>4.915154397524811e-09</v>
+        <v>6.553539196699748e-09</v>
       </c>
     </row>
     <row r="13">
@@ -1165,7 +1165,7 @@
         <v>0.0006845637960723105</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001026845694108466</v>
+        <v>0.001232214832930159</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -530,34 +530,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D2" t="n">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="E2" t="n">
         <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.835</v>
+        <v>0.8370833333333333</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8683314415437003</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7318007662835249</v>
+        <v>0.7355769230769231</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7941787941787941</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D3" t="n">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="E3" t="n">
         <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9008333333333334</v>
+        <v>0.9029166666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>1.783615866938336e-11</v>
+        <v>1.293825463246631e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>8.02627140122251e-11</v>
+        <v>5.822214584609839e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9206680584551148</v>
+        <v>0.9207507820646507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002426192852128931</v>
+        <v>0.000243017363431645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003119390809880054</v>
+        <v>0.0003124508958406864</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8490384615384615</v>
       </c>
       <c r="N3" t="n">
-        <v>3.02765131940777e-10</v>
+        <v>2.08004379467488e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.362443093733496e-09</v>
+        <v>9.360197076036958e-10</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8811188811188811</v>
+        <v>0.8834417208604302</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.26986545870891e-13</v>
+        <v>8.814770338615721e-14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.142878912838019e-12</v>
+        <v>7.933293304754149e-13</v>
       </c>
     </row>
     <row r="4">
@@ -630,52 +630,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D4" t="n">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="E4" t="n">
         <v>115</v>
       </c>
       <c r="F4" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8783333333333333</v>
+        <v>0.8804166666666666</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14590095118893e-05</v>
+        <v>1.908079968654252e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.862621712140074e-05</v>
+        <v>3.434543943577653e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8828920570264766</v>
+        <v>0.8830111902339777</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3601858815961053</v>
+        <v>0.360234376412101</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3601858815961053</v>
+        <v>0.360234376412101</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8304597701149425</v>
+        <v>0.8346153846153846</v>
       </c>
       <c r="N4" t="n">
-        <v>6.088424542278483e-08</v>
+        <v>4.668876395841681e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.826527362683545e-07</v>
+        <v>1.400662918752504e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8558736426456071</v>
+        <v>0.8581314878892734</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.618082810248584e-07</v>
+        <v>3.092945780440225e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>8.140686323059314e-07</v>
+        <v>6.959128005990506e-07</v>
       </c>
     </row>
     <row r="5">
@@ -691,49 +691,49 @@
         <v>833</v>
       </c>
       <c r="D5" t="n">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="E5" t="n">
         <v>165</v>
       </c>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8433333333333334</v>
+        <v>0.845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4553901067585051</v>
+        <v>0.4773732474457597</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5855015658323637</v>
+        <v>0.6137656038588339</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04453936442729994</v>
+        <v>0.04447699627698107</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05010678498071244</v>
+        <v>0.0500366208116037</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7978927203065134</v>
+        <v>0.8009615384615385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004429715057418754</v>
+        <v>0.0004906430856627067</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0005695347930966969</v>
+        <v>0.00063082682442348</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8158667972575906</v>
+        <v>0.817468105986261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09191483445756859</v>
+        <v>0.09839988336798541</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1181762157311596</v>
+        <v>0.1265141357588384</v>
       </c>
     </row>
     <row r="6">
@@ -746,34 +746,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D6" t="n">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="E6" t="n">
         <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7966666666666666</v>
+        <v>0.79875</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7785571142284569</v>
+        <v>0.7787787787787788</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7442528735632183</v>
+        <v>0.7480769230769231</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7610186092066601</v>
+        <v>0.7631191760666994</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -788,52 +788,52 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D7" t="n">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="E7" t="n">
         <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="G7" t="n">
-        <v>0.85125</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>8.031929076040189e-07</v>
+        <v>7.122328621674807e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.807184042109043e-06</v>
+        <v>1.602523939876832e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9364675984752223</v>
+        <v>0.9365482233502538</v>
       </c>
       <c r="K7" t="n">
-        <v>1.09536713296107e-21</v>
+        <v>1.099593915820541e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>4.929152098324816e-21</v>
+        <v>4.948172621192436e-21</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7059386973180076</v>
+        <v>0.7096153846153846</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0558672218848466</v>
+        <v>0.05435521753337321</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05586722188484659</v>
+        <v>0.05435521753337321</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8050245767340252</v>
+        <v>0.8074398249452955</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0009273099621365588</v>
+        <v>0.0008732091337347716</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001390964943204838</v>
+        <v>0.001309813700602158</v>
       </c>
     </row>
     <row r="8">
@@ -846,52 +846,52 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D8" t="n">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E8" t="n">
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G8" t="n">
-        <v>0.82875</v>
+        <v>0.8308333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004909853445594204</v>
+        <v>0.004726900766926011</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007364780168391307</v>
+        <v>0.007090351150389018</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9502133712660028</v>
+        <v>0.9502840909090909</v>
       </c>
       <c r="K8" t="n">
-        <v>5.768561548496698e-25</v>
+        <v>5.727272398079546e-25</v>
       </c>
       <c r="L8" t="n">
-        <v>5.191705393647028e-24</v>
+        <v>5.154545158271591e-24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6398467432950191</v>
+        <v>0.6432692307692308</v>
       </c>
       <c r="N8" t="n">
-        <v>2.919623911647553e-07</v>
+        <v>2.526374606694628e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>6.569153801206996e-07</v>
+        <v>5.684342865062914e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7647395535203205</v>
+        <v>0.7672018348623854</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8182340598783613</v>
+        <v>0.7877757379679886</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8182340598783613</v>
+        <v>0.7877757379679886</v>
       </c>
     </row>
     <row r="9">
@@ -904,52 +904,52 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D9" t="n">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="E9" t="n">
         <v>117</v>
       </c>
       <c r="F9" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8704166666666666</v>
+        <v>0.8729166666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>7.758263820081272e-12</v>
+        <v>4.478335586909986e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>6.982437438073145e-11</v>
+        <v>4.030502028218988e-11</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8790072388831437</v>
+        <v>0.8792569659442725</v>
       </c>
       <c r="K9" t="n">
-        <v>3.800483870308596e-09</v>
+        <v>3.811176829356442e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.140145161092579e-08</v>
+        <v>1.143353048806932e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.814176245210728</v>
+        <v>0.8192307692307692</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001420109393108276</v>
+        <v>9.869117474931823e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002556196907594897</v>
+        <v>0.0001776441145487728</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8453505718547986</v>
+        <v>0.848183175709308</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66488425149846e-11</v>
+        <v>7.55659456010177e-12</v>
       </c>
       <c r="R9" t="n">
-        <v>7.491979131743069e-11</v>
+        <v>3.400467552045797e-11</v>
       </c>
     </row>
     <row r="10">
@@ -965,16 +965,16 @@
         <v>688</v>
       </c>
       <c r="D10" t="n">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="E10" t="n">
         <v>175</v>
       </c>
       <c r="F10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7787500000000001</v>
+        <v>0.7804166666666666</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -984,12 +984,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.6590038314176245</v>
+        <v>0.6615384615384615</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.7215521761929733</v>
+        <v>0.7230688386757751</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1007,22 +1007,22 @@
         <v>611</v>
       </c>
       <c r="D11" t="n">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="E11" t="n">
         <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7854166666666667</v>
+        <v>0.7870833333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5999831421697411</v>
+        <v>0.5989705017913463</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6749810349409587</v>
+        <v>0.6738418145152645</v>
       </c>
       <c r="J11" t="n">
         <v>0.8816738816738817</v>
@@ -1034,22 +1034,22 @@
         <v>1.344948103226681e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5852490421455939</v>
+        <v>0.5875</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005987452412680276</v>
+        <v>0.0005750077137896216</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006735883964265311</v>
+        <v>0.0006468836780133243</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7035118019573979</v>
+        <v>0.705135603000577</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2407683837052523</v>
+        <v>0.2395327619188886</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2708644316684089</v>
+        <v>0.2694743571587497</v>
       </c>
     </row>
     <row r="12">
@@ -1065,22 +1065,22 @@
         <v>605</v>
       </c>
       <c r="D12" t="n">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="E12" t="n">
         <v>269</v>
       </c>
       <c r="F12" t="n">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="G12" t="n">
-        <v>0.705</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>6.154608721883135e-09</v>
+        <v>5.713791637834985e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>1.84638261656494e-08</v>
+        <v>1.714137491350495e-08</v>
       </c>
       <c r="J12" t="n">
         <v>0.6922196796338673</v>
@@ -1092,22 +1092,22 @@
         <v>1.198798211129372e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5795019157088123</v>
+        <v>0.5817307692307693</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0002172866910617807</v>
+        <v>0.0002075157196352684</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003259300365926711</v>
+        <v>0.0003112735794529026</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6308654848800835</v>
+        <v>0.632183908045977</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.184513065566583e-09</v>
+        <v>2.013179676811879e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>6.553539196699748e-09</v>
+        <v>6.039539030435637e-09</v>
       </c>
     </row>
     <row r="13">
@@ -1123,22 +1123,22 @@
         <v>870</v>
       </c>
       <c r="D13" t="n">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="E13" t="n">
         <v>352</v>
       </c>
       <c r="F13" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7808333333333334</v>
+        <v>0.7825</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8891975855015103</v>
+        <v>0.8888965749800711</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8891975855015103</v>
+        <v>0.888896574980071</v>
       </c>
       <c r="J13" t="n">
         <v>0.7119476268412439</v>
@@ -1150,22 +1150,22 @@
         <v>1.572058032039625e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="N13" t="n">
-        <v>4.623550295738242e-20</v>
+        <v>2.777277430834444e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>4.161195266164418e-19</v>
+        <v>2.499549687751e-19</v>
       </c>
       <c r="P13" t="n">
-        <v>0.767872903795234</v>
+        <v>0.7692307692307694</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0006845637960723105</v>
+        <v>0.0006630724429171291</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001232214832930159</v>
+        <v>0.001193530397250832</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D2" t="n">
         <v>1244</v>
@@ -539,25 +539,25 @@
         <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8370833333333333</v>
+        <v>0.8366666666666667</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8683314415437003</v>
+        <v>0.8681818181818182</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7355769230769231</v>
+        <v>0.7346153846153847</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7964601769911505</v>
+        <v>0.7958333333333333</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D3" t="n">
         <v>1284</v>
@@ -581,43 +581,43 @@
         <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9029166666666667</v>
+        <v>0.9025</v>
       </c>
       <c r="H3" t="n">
-        <v>1.293825463246631e-11</v>
+        <v>1.380814341177806e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>5.822214584609839e-11</v>
+        <v>6.213664535300129e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9207507820646507</v>
+        <v>0.9206680584551148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000243017363431645</v>
+        <v>0.0002426192852128931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003124508958406864</v>
+        <v>0.0003119390809880054</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8490384615384615</v>
+        <v>0.8480769230769231</v>
       </c>
       <c r="N3" t="n">
-        <v>2.08004379467488e-10</v>
+        <v>2.236178641159215e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>9.360197076036958e-10</v>
+        <v>1.006280388521647e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8834417208604302</v>
+        <v>0.8828828828828829</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.814770338615721e-14</v>
+        <v>9.439472540453342e-14</v>
       </c>
       <c r="R3" t="n">
-        <v>7.933293304754149e-13</v>
+        <v>8.495525286408007e-13</v>
       </c>
     </row>
     <row r="4">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D4" t="n">
         <v>1245</v>
@@ -639,43 +639,43 @@
         <v>115</v>
       </c>
       <c r="F4" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8804166666666666</v>
+        <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>1.908079968654252e-05</v>
+        <v>1.953989911286258e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.434543943577653e-05</v>
+        <v>3.517181840315265e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8830111902339777</v>
+        <v>0.8828920570264766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.360234376412101</v>
+        <v>0.3601858815961053</v>
       </c>
       <c r="L4" t="n">
-        <v>0.360234376412101</v>
+        <v>0.3601858815961053</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8346153846153846</v>
+        <v>0.8336538461538462</v>
       </c>
       <c r="N4" t="n">
-        <v>4.668876395841681e-08</v>
+        <v>4.912371043315823e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.400662918752504e-07</v>
+        <v>1.473711312994747e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8581314878892734</v>
+        <v>0.8575667655786351</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.092945780440225e-07</v>
+        <v>3.183481999590376e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>6.959128005990506e-07</v>
+        <v>7.162834499078345e-07</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4773732474457597</v>
+        <v>0.4534878187240389</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6137656038588339</v>
+        <v>0.5830557669309071</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04447699627698107</v>
+        <v>0.04453936442729994</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0500366208116037</v>
+        <v>0.05010678498071244</v>
       </c>
       <c r="M5" t="n">
         <v>0.8009615384615385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004906430856627067</v>
+        <v>0.0004071594504748587</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00063082682442348</v>
+        <v>0.000523490722039104</v>
       </c>
       <c r="P5" t="n">
         <v>0.817468105986261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09839988336798541</v>
+        <v>0.09056662436074937</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1265141357588384</v>
+        <v>0.1164428027495349</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D6" t="n">
         <v>1139</v>
@@ -755,25 +755,25 @@
         <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G6" t="n">
-        <v>0.79875</v>
+        <v>0.7983333333333333</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7787787787787788</v>
+        <v>0.7785571142284569</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7480769230769231</v>
+        <v>0.7471153846153846</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7631191760666994</v>
+        <v>0.7625122669283612</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -803,37 +803,37 @@
         <v>0.8533333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>7.122328621674807e-07</v>
+        <v>5.917596505499416e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.602523939876832e-06</v>
+        <v>1.331459213737368e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9365482233502538</v>
       </c>
       <c r="K7" t="n">
-        <v>1.099593915820541e-21</v>
+        <v>1.079270655249006e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>4.948172621192436e-21</v>
+        <v>4.856717948620526e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7096153846153846</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05435521753337321</v>
+        <v>0.0609870468096286</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05435521753337321</v>
+        <v>0.0609870468096286</v>
       </c>
       <c r="P7" t="n">
         <v>0.8074398249452955</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0008732091337347716</v>
+        <v>0.0007609523671805884</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001309813700602158</v>
+        <v>0.001141428550770883</v>
       </c>
     </row>
     <row r="8">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D8" t="n">
         <v>1325</v>
@@ -855,43 +855,43 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8308333333333333</v>
+        <v>0.8304166666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004726900766926011</v>
+        <v>0.004763275243764411</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007090351150389018</v>
+        <v>0.007144912865646617</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9502840909090909</v>
+        <v>0.9502133712660028</v>
       </c>
       <c r="K8" t="n">
-        <v>5.727272398079546e-25</v>
+        <v>5.768561548496698e-25</v>
       </c>
       <c r="L8" t="n">
-        <v>5.154545158271591e-24</v>
+        <v>5.191705393647028e-24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6432692307692308</v>
+        <v>0.6423076923076924</v>
       </c>
       <c r="N8" t="n">
-        <v>2.526374606694628e-07</v>
+        <v>2.589504672899557e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>5.684342865062914e-07</v>
+        <v>5.826385514024003e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7672018348623854</v>
+        <v>0.7664945496270796</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7877757379679886</v>
+        <v>0.7879463836477409</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7877757379679886</v>
+        <v>0.7879463836477409</v>
       </c>
     </row>
     <row r="9">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D9" t="n">
         <v>1243</v>
@@ -913,43 +913,43 @@
         <v>117</v>
       </c>
       <c r="F9" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8729166666666667</v>
+        <v>0.8720833333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>4.478335586909986e-12</v>
+        <v>6.37001977468192e-12</v>
       </c>
       <c r="I9" t="n">
-        <v>4.030502028218988e-11</v>
+        <v>5.733017797213728e-11</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8792569659442725</v>
+        <v>0.8790072388831437</v>
       </c>
       <c r="K9" t="n">
-        <v>3.811176829356442e-09</v>
+        <v>3.800483870308596e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.143353048806932e-08</v>
+        <v>1.140145161092579e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8192307692307692</v>
+        <v>0.8173076923076923</v>
       </c>
       <c r="N9" t="n">
-        <v>9.869117474931823e-05</v>
+        <v>0.0001276446023527544</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0001776441145487728</v>
+        <v>0.0002297602842349579</v>
       </c>
       <c r="P9" t="n">
-        <v>0.848183175709308</v>
+        <v>0.8470353761833581</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.55659456010177e-12</v>
+        <v>1.081525365254213e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>3.400467552045797e-11</v>
+        <v>4.866864143643958e-11</v>
       </c>
     </row>
     <row r="10">
@@ -1165,7 +1165,7 @@
         <v>0.0006630724429171291</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001193530397250832</v>
+        <v>0.001141428550770883</v>
       </c>
     </row>
   </sheetData>

--- a/eval/results/evaluation_metrics_fisher_full150.xlsx
+++ b/eval/results/evaluation_metrics_fisher_full150.xlsx
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="D2" t="n">
         <v>1244</v>
@@ -539,25 +539,25 @@
         <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8366666666666667</v>
+        <v>0.8379166666666666</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8681818181818182</v>
+        <v>0.8686296715741789</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>0.7346153846153847</v>
+        <v>0.7375</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>0.7958333333333333</v>
+        <v>0.797711908476339</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D3" t="n">
         <v>1284</v>
@@ -581,43 +581,43 @@
         <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9025</v>
+        <v>0.9029166666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>1.380814341177806e-11</v>
+        <v>2.207035938454956e-11</v>
       </c>
       <c r="I3" t="n">
-        <v>6.213664535300129e-11</v>
+        <v>9.931661723047303e-11</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9206680584551148</v>
+        <v>0.9207507820646507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0002426192852128931</v>
+        <v>0.0003160912345778657</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003119390809880054</v>
+        <v>0.0004064030158858274</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8480769230769231</v>
+        <v>0.8490384615384615</v>
       </c>
       <c r="N3" t="n">
-        <v>2.236178641159215e-10</v>
+        <v>3.934477155453887e-10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.006280388521647e-09</v>
+        <v>1.770514719954249e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8828828828828829</v>
+        <v>0.8834417208604302</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.439472540453342e-14</v>
+        <v>2.159146574448229e-13</v>
       </c>
       <c r="R3" t="n">
-        <v>8.495525286408007e-13</v>
+        <v>1.943231917003406e-12</v>
       </c>
     </row>
     <row r="4">
@@ -645,37 +645,37 @@
         <v>0.88</v>
       </c>
       <c r="H4" t="n">
-        <v>1.953989911286258e-05</v>
+        <v>3.280902437900651e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.517181840315265e-05</v>
+        <v>5.905624388221173e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.8828920570264766</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3601858815961053</v>
+        <v>0.3607633245789883</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3601858815961053</v>
+        <v>0.3607633245789883</v>
       </c>
       <c r="M4" t="n">
         <v>0.8336538461538462</v>
       </c>
       <c r="N4" t="n">
-        <v>4.912371043315823e-08</v>
+        <v>1.120029559232957e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.473711312994747e-07</v>
+        <v>3.36008867769887e-07</v>
       </c>
       <c r="P4" t="n">
         <v>0.8575667655786351</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.183481999590376e-07</v>
+        <v>7.345416629274237e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>7.162834499078345e-07</v>
+        <v>1.652718741586703e-06</v>
       </c>
     </row>
     <row r="5">
@@ -703,37 +703,37 @@
         <v>0.845</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4534878187240389</v>
+        <v>0.5272215527476609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5830557669309071</v>
+        <v>0.6778562821041355</v>
       </c>
       <c r="J5" t="n">
         <v>0.8346693386773547</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04453936442729994</v>
+        <v>0.04441989136440894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05010678498071244</v>
+        <v>0.04997237778496005</v>
       </c>
       <c r="M5" t="n">
         <v>0.8009615384615385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004071594504748587</v>
+        <v>0.0007080115956736204</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000523490722039104</v>
+        <v>0.0007965130451328229</v>
       </c>
       <c r="P5" t="n">
         <v>0.817468105986261</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.09056662436074937</v>
+        <v>0.1157921121265197</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1164428027495349</v>
+        <v>0.1488755727340968</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D6" t="n">
         <v>1139</v>
@@ -755,25 +755,25 @@
         <v>221</v>
       </c>
       <c r="F6" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7983333333333333</v>
+        <v>0.7991666666666667</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>0.7785571142284569</v>
+        <v>0.779</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>0.7471153846153846</v>
+        <v>0.7490384615384615</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>0.7625122669283612</v>
+        <v>0.7637254901960784</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -803,37 +803,37 @@
         <v>0.8533333333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>5.917596505499416e-07</v>
+        <v>8.562936323077191e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.331459213737368e-06</v>
+        <v>1.926660672692368e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.9365482233502538</v>
       </c>
       <c r="K7" t="n">
-        <v>1.079270655249006e-21</v>
+        <v>1.127669984450169e-21</v>
       </c>
       <c r="L7" t="n">
-        <v>4.856717948620526e-21</v>
+        <v>5.07451493002576e-21</v>
       </c>
       <c r="M7" t="n">
         <v>0.7096153846153846</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0609870468096286</v>
+        <v>0.04832921116343653</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0609870468096286</v>
+        <v>0.04832921116343653</v>
       </c>
       <c r="P7" t="n">
         <v>0.8074398249452955</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007609523671805884</v>
+        <v>0.001001139144887943</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001141428550770883</v>
+        <v>0.001501708717331915</v>
       </c>
     </row>
     <row r="8">
@@ -861,37 +861,37 @@
         <v>0.8304166666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004763275243764411</v>
+        <v>0.005947489389372665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.007144912865646617</v>
+        <v>0.008921234084058998</v>
       </c>
       <c r="J8" t="n">
         <v>0.9502133712660028</v>
       </c>
       <c r="K8" t="n">
-        <v>5.768561548496698e-25</v>
+        <v>1.010731856565944e-24</v>
       </c>
       <c r="L8" t="n">
-        <v>5.191705393647028e-24</v>
+        <v>9.096586709093496e-24</v>
       </c>
       <c r="M8" t="n">
         <v>0.6423076923076924</v>
       </c>
       <c r="N8" t="n">
-        <v>2.589504672899557e-07</v>
+        <v>1.508019064518737e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>5.826385514024003e-07</v>
+        <v>3.393042895167158e-07</v>
       </c>
       <c r="P8" t="n">
         <v>0.7664945496270796</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7879463836477409</v>
+        <v>0.8475753501009612</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7879463836477409</v>
+        <v>0.8475753501009612</v>
       </c>
     </row>
     <row r="9">
@@ -919,37 +919,37 @@
         <v>0.8720833333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>6.37001977468192e-12</v>
+        <v>1.049649379879613e-11</v>
       </c>
       <c r="I9" t="n">
-        <v>5.733017797213728e-11</v>
+        <v>9.446844418916515e-11</v>
       </c>
       <c r="J9" t="n">
         <v>0.8790072388831437</v>
       </c>
       <c r="K9" t="n">
-        <v>3.800483870308596e-09</v>
+        <v>3.87687132044137e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.140145161092579e-08</v>
+        <v>1.163061396132411e-08</v>
       </c>
       <c r="M9" t="n">
         <v>0.8173076923076923</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0001276446023527544</v>
+        <v>0.0001913220486012389</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0002297602842349579</v>
+        <v>0.0002869830729018584</v>
       </c>
       <c r="P9" t="n">
         <v>0.8470353761833581</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.081525365254213e-11</v>
+        <v>2.295058397350061e-11</v>
       </c>
       <c r="R9" t="n">
-        <v>4.866864143643958e-11</v>
+        <v>1.032776278807528e-10</v>
       </c>
     </row>
     <row r="10">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D10" t="n">
         <v>1185</v>
@@ -971,25 +971,25 @@
         <v>175</v>
       </c>
       <c r="F10" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7804166666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>0.7972190034762456</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.6634615384615384</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0.7230688386757751</v>
+        <v>0.7244094488188977</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1019,37 +1019,37 @@
         <v>0.7870833333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5989705017913463</v>
+        <v>0.6483318120255308</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6738418145152645</v>
+        <v>0.7293732885287222</v>
       </c>
       <c r="J11" t="n">
         <v>0.8816738816738817</v>
       </c>
       <c r="K11" t="n">
-        <v>7.471933906814893e-06</v>
+        <v>7.645931260329023e-06</v>
       </c>
       <c r="L11" t="n">
-        <v>1.344948103226681e-05</v>
+        <v>1.271771987047257e-05</v>
       </c>
       <c r="M11" t="n">
         <v>0.5875</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0005750077137896216</v>
+        <v>0.0004067242207159452</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006468836780133243</v>
+        <v>0.000522931140920501</v>
       </c>
       <c r="P11" t="n">
         <v>0.705135603000577</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2395327619188886</v>
+        <v>0.2111277101924791</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2694743571587497</v>
+        <v>0.237518673966539</v>
       </c>
     </row>
     <row r="12">
@@ -1077,37 +1077,37 @@
         <v>0.7066666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>5.713791637834985e-09</v>
+        <v>3.758935090240073e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>1.714137491350495e-08</v>
+        <v>1.127680527072022e-08</v>
       </c>
       <c r="J12" t="n">
         <v>0.6922196796338673</v>
       </c>
       <c r="K12" t="n">
-        <v>5.327992049463875e-07</v>
+        <v>5.24179716879588e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>1.198798211129372e-06</v>
+        <v>1.179404362979073e-06</v>
       </c>
       <c r="M12" t="n">
         <v>0.5817307692307693</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0002075157196352684</v>
+        <v>0.0001434126232102297</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0003112735794529026</v>
+        <v>0.0002581427217784135</v>
       </c>
       <c r="P12" t="n">
         <v>0.632183908045977</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.013179676811879e-09</v>
+        <v>1.053853816781084e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>6.039539030435637e-09</v>
+        <v>3.161561450343253e-09</v>
       </c>
     </row>
     <row r="13">
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D13" t="n">
         <v>1008</v>
@@ -1129,43 +1129,43 @@
         <v>352</v>
       </c>
       <c r="F13" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7825</v>
+        <v>0.7829166666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8888965749800711</v>
+        <v>0.9164681943338163</v>
       </c>
       <c r="I13" t="n">
-        <v>0.888896574980071</v>
+        <v>0.9164681943338162</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7119476268412439</v>
+        <v>0.7121831561733443</v>
       </c>
       <c r="K13" t="n">
-        <v>1.048038688026416e-05</v>
+        <v>8.478479913648376e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>1.572058032039625e-05</v>
+        <v>1.271771987047257e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8365384615384616</v>
+        <v>0.8375</v>
       </c>
       <c r="N13" t="n">
-        <v>2.777277430834444e-20</v>
+        <v>3.785194724895531e-20</v>
       </c>
       <c r="O13" t="n">
-        <v>2.499549687751e-19</v>
+        <v>3.406675252405978e-19</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7692307692307694</v>
+        <v>0.7697746354396818</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0006630724429171291</v>
+        <v>0.000849143087229431</v>
       </c>
       <c r="R13" t="n">
-        <v>0.001141428550770883</v>
+        <v>0.001501708717331915</v>
       </c>
     </row>
   </sheetData>
